--- a/assessment/templates/entra-global-admin-checklist.xlsx
+++ b/assessment/templates/entra-global-admin-checklist.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>App ID Accuracy: Verify all CA policies targeting Copilot reference the correct Enterprise Copilot Platform App ID: `fb8d773d-7ef8-4ec0-a117-179f88add510`; May 2026 Enforcement Audit: Confirm CA policy audit for "All resources + exclusion" patterns has been completed; document remediation actions taken; MFA Enforcement: Attempt to access Copilot without MFA — confirm access is blocked and MFA prompt is presented; Device Compliance: Attempt to access Copilot from a non-compliant or unmanaged device — confirm access is blocked; Location Restriction: Test Copilot access from an IP address outside named locations — confirm access is blocked (Recommended/Regulated levels); Risk-Based Blocking: Simulate a risky sign-in (use Entra ID Protection test tools) — confirm Copilot access is blocked when sign-in risk is medium or high; Session Controls: Access Copilot and wait for the sign-in frequency interval to expire — confirm re-authentication is required; Adaptive Protection Integration: Verify Adaptive Protection is enabled and that IRM risk level changes trigger corresponding CA policy enforcement for Copilot access; Break-Glass Exclusion: Confirm break-glass accounts are excluded from Copilot CA policies and that exclusion is documented; Audit Logging: Verify that Conditional Access policy evaluation results (success, failure, not applied) appear in the Entra sign-in logs; Report-Only Testing: Before enabling enforcement, confirm policies have been tested in report-only mode for at least 7 days with acceptable results; Policy Documentation: Confirm Conditional Access policy inventory is maintained and includes last review date, policy purpose, and exception justifications</t>
+          <t>CA policy export targeting Copilot / Office 365 app registrations; MFA enforcement evidence for Copilot-eligible users; Device compliance requirement configuration; Location-based restriction configuration (if applicable)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Segment Assignment: Verify that all Copilot-licensed users are assigned to appropriate organizational segments with no gaps or misassignments; Policy Application Status: Confirm all information barrier policies show "Active" and "Applied" status; Copilot Chat Barrier Enforcement: As an Investment Banking user, query Copilot Chat for research content — confirm no cross-segment results are returned; File Grounding Restriction: Attempt to reference a Research segment file in Copilot while signed in as an Investment Banking user — confirm Copilot cannot access the file; Teams Copilot Barrier Enforcement: Verify that Teams Copilot meeting summaries do not include content from barrier-separated participants; Channel Agent IB Gap Documentation: Confirm that Channel Agent deployments are documented with IB segment membership audits for each channel; confirm no Channel Agents are deployed in channels with mixed IB-segment membership; confirm the Channel Agent IB limitation is documented in supervisory procedures; Channel Agent Compensating Controls: Verify that sensitivity labels are applied to content in channels where Channel Agent is deployed adjacent to IB segments; confirm DSPM for AI monitoring is configured for Channel Agent activity; SharePoint IB Mode: Confirm SharePoint sites have appropriate IB modes applied and that Copilot in SharePoint respects barrier boundaries; Temporary Barrier Activation: Create a test temporary barrier and verify Copilot enforcement within 1 hour of policy application; Supervisory Access: Verify that Compliance segment users can access content across barriers as designed, and that access is logged; Barrier Event Audit Logs: Confirm that information barrier policy match events appear in the Unified Audit Log; Periodic Validation: Confirm quarterly barrier validation testing is scheduled, documented, and reviewed by compliance</t>
+          <t>IB policy configuration export with segment definitions; Test results showing Copilot honors IB boundaries; Segment membership review cadence documentation; Ethical-wall compliance evidence for examiner response</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Endpoint Documentation: Verify that M365/Copilot network endpoints are documented in the firewall management system and are current; Firewall Rules: Confirm firewall rules allow required M365 traffic and block unnecessary endpoints (e.g., Bing if web search disabled); TLS Verification: Confirm that all Copilot traffic uses TLS 1.2 or higher — test from representative network locations; Location-Based CA: Access Copilot from outside named locations — verify Conditional Access blocks or requires additional authentication; GSA Deployment (if applicable): Verify Global Secure Access client is deployed to managed devices and M365 traffic is routed through GSA; Tenant Restrictions: Attempt to sign into a personal M365 tenant from a managed device — verify access is blocked or restricted; SSL Inspection Bypass: Verify that M365 endpoints are excluded from SSL inspection proxy processing; Network Segmentation: For trading floor environments, verify that Copilot traffic is appropriately segmented and logged; Network Monitoring: Confirm that Copilot-related network traffic is included in SOC monitoring scope; Documentation: Verify that network architecture documentation includes Copilot traffic paths and is included in examination readiness materials</t>
+          <t>Named location configuration for Copilot CA policies; Private Link configuration (if applicable); Network security policy alignment documentation</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>

--- a/assessment/templates/entra-global-admin-checklist.xlsx
+++ b/assessment/templates/entra-global-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.4  |  3 controls</t>
+          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.8  |  3 controls</t>
         </is>
       </c>
     </row>

--- a/assessment/templates/entra-global-admin-checklist.xlsx
+++ b/assessment/templates/entra-global-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.8  |  3 controls</t>
+          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.8.0  |  3 controls</t>
         </is>
       </c>
     </row>

--- a/assessment/templates/entra-global-admin-checklist.xlsx
+++ b/assessment/templates/entra-global-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.4  |  3 controls</t>
+          <t>Role: Entra Global Admin  |  FSI Copilot Governance Framework v1.8.0  |  3 controls</t>
         </is>
       </c>
     </row>

--- a/assessment/templates/entra-global-admin-checklist.xlsx
+++ b/assessment/templates/entra-global-admin-checklist.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Conditional Access Policies for Copilot Workloads</t>
+          <t>Are Conditional Access policies for Copilot workloads configured and reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Information Barriers for Copilot (Chinese Wall)</t>
+          <t>Are Information Barrier policies configured and tested for Copilot content surfacing across ethical-wall segments?</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Network Security and Private Connectivity</t>
+          <t>Are network security controls (Conditional Access named locations, Global Secure Access, tenant restrictions) configured for Copilot workloads per the organization's network security policy?</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Named location configuration for Copilot CA policies; Private Link configuration (if applicable); Network security policy alignment documentation</t>
+          <t>Named location configuration for Copilot CA policies; Private Link configuration for adjacent Azure resources (if applicable); Network security policy alignment documentation</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
